--- a/telehealth_forms/005_child_concerns_report_form--telehealth_forms.xlsx
+++ b/telehealth_forms/005_child_concerns_report_form--telehealth_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'behavioral_issues',_'value':_'behavioral'}</t>
+          <t>behavioral_issues</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Behavioral Issues', 'value': 'behavioral'}</t>
+          <t>Behavioral Issues</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'academic_performance',_'value':_'academic'}</t>
+          <t>academic_performance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Performance', 'value': 'academic'}</t>
+          <t>Academic Performance</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'social_interactions',_'value':_'social'}</t>
+          <t>social_interactions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Social Interactions', 'value': 'social'}</t>
+          <t>Social Interactions</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'physical_wellbeing',_'value':_'physical'}</t>
+          <t>physical_wellbeing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Wellbeing', 'value': 'physical'}</t>
+          <t>Physical Wellbeing</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_notified',_'value':_true}</t>
+          <t>yes_-_notified</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Notified', 'value': True}</t>
+          <t>Yes - Notified</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_pending_review',_'value':_false}</t>
+          <t>no_-_pending_review</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No - Pending Review', 'value': False}</t>
+          <t>No - Pending Review</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
